--- a/5. Knife/output/Rugosity_growth_param_0.5.xlsx
+++ b/5. Knife/output/Rugosity_growth_param_0.5.xlsx
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9633199139642454</v>
+        <v>0.9761427918366682</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9869537449534416</v>
+        <v>1.014619340494381</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.028763125183674</v>
+        <v>1.071599604703591</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.089829545046695</v>
+        <v>1.15336736747316</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.211465320019592</v>
+        <v>1.307389553628232</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.381660452110839</v>
+        <v>1.513437027939903</v>
       </c>
     </row>
     <row r="9">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.595153328313126</v>
+        <v>1.762572405710143</v>
       </c>
     </row>
     <row r="10">
@@ -504,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.843682188266042</v>
+        <v>2.038728492147448</v>
       </c>
     </row>
     <row r="11">
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.111278598272982</v>
+        <v>2.31877745835498</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.37757980522342</v>
+        <v>2.588658960884703</v>
       </c>
     </row>
     <row r="13">
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.625534931817974</v>
+        <v>2.834043952901044</v>
       </c>
     </row>
     <row r="14">
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.830988369336215</v>
+        <v>3.025213583326727</v>
       </c>
     </row>
     <row r="15">
@@ -544,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.993300405083571</v>
+        <v>3.180391088062339</v>
       </c>
     </row>
     <row r="16">
@@ -552,7 +552,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.074989007134332</v>
+        <v>2.239405036883532</v>
       </c>
     </row>
   </sheetData>
